--- a/サービス担当者会議.xlsx
+++ b/サービス担当者会議.xlsx
@@ -748,57 +748,27 @@
     <xf numFmtId="31" fontId="6" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -860,6 +830,36 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1229,11 +1229,11 @@
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
-      <c r="J3" s="25" t="s">
+      <c r="J3" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="K3" s="25"/>
-      <c r="L3" s="25"/>
+      <c r="K3" s="10"/>
+      <c r="L3" s="10"/>
       <c r="M3" s="6"/>
       <c r="N3" s="7" t="s">
         <v>17</v>
@@ -1248,10 +1248,10 @@
       </c>
     </row>
     <row r="4" spans="1:18" ht="22.8" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="46" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="17"/>
+      <c r="B4" s="46"/>
       <c r="C4" s="49"/>
       <c r="D4" s="49"/>
       <c r="E4" s="49"/>
@@ -1259,11 +1259,11 @@
       <c r="G4" s="49"/>
       <c r="H4" s="49"/>
       <c r="I4" s="4"/>
-      <c r="J4" s="25" t="s">
+      <c r="J4" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="K4" s="25"/>
-      <c r="L4" s="25"/>
+      <c r="K4" s="10"/>
+      <c r="L4" s="10"/>
       <c r="M4" s="48"/>
       <c r="N4" s="48"/>
       <c r="O4" s="48"/>
@@ -1272,10 +1272,10 @@
       <c r="R4" s="48"/>
     </row>
     <row r="5" spans="1:18" ht="22.8" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="17" t="s">
+      <c r="A5" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="17"/>
+      <c r="B5" s="46"/>
       <c r="C5" s="9"/>
       <c r="D5" s="9" t="s">
         <v>20</v>
@@ -1289,17 +1289,17 @@
         <v>22</v>
       </c>
       <c r="I5" s="5"/>
-      <c r="J5" s="25" t="s">
+      <c r="J5" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="K5" s="25"/>
-      <c r="L5" s="25"/>
-      <c r="M5" s="26"/>
-      <c r="N5" s="26"/>
-      <c r="O5" s="26"/>
-      <c r="P5" s="26"/>
-      <c r="Q5" s="26"/>
-      <c r="R5" s="26"/>
+      <c r="K5" s="10"/>
+      <c r="L5" s="10"/>
+      <c r="M5" s="11"/>
+      <c r="N5" s="11"/>
+      <c r="O5" s="11"/>
+      <c r="P5" s="11"/>
+      <c r="Q5" s="11"/>
+      <c r="R5" s="11"/>
     </row>
     <row r="6" spans="1:18" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4"/>
@@ -1322,204 +1322,204 @@
       <c r="R6" s="4"/>
     </row>
     <row r="7" spans="1:18" ht="22.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="44" t="s">
+      <c r="A7" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="45"/>
-      <c r="C7" s="10" t="s">
+      <c r="B7" s="35"/>
+      <c r="C7" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="11"/>
-      <c r="E7" s="24" t="s">
+      <c r="D7" s="16"/>
+      <c r="E7" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="F7" s="12"/>
-      <c r="G7" s="13"/>
-      <c r="H7" s="10" t="s">
+      <c r="F7" s="13"/>
+      <c r="G7" s="14"/>
+      <c r="H7" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="I7" s="11"/>
-      <c r="J7" s="12" t="s">
+      <c r="I7" s="16"/>
+      <c r="J7" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="K7" s="12"/>
-      <c r="L7" s="13"/>
-      <c r="M7" s="10" t="s">
+      <c r="K7" s="13"/>
+      <c r="L7" s="14"/>
+      <c r="M7" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="N7" s="11"/>
-      <c r="O7" s="24" t="s">
+      <c r="N7" s="16"/>
+      <c r="O7" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="P7" s="12"/>
-      <c r="Q7" s="12"/>
-      <c r="R7" s="13"/>
+      <c r="P7" s="13"/>
+      <c r="Q7" s="13"/>
+      <c r="R7" s="14"/>
     </row>
     <row r="8" spans="1:18" ht="22.8" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="46"/>
-      <c r="B8" s="47"/>
-      <c r="C8" s="19" t="s">
+      <c r="A8" s="36"/>
+      <c r="B8" s="37"/>
+      <c r="C8" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="20"/>
-      <c r="E8" s="21"/>
-      <c r="F8" s="22"/>
-      <c r="G8" s="23"/>
-      <c r="H8" s="14" t="s">
+      <c r="D8" s="39"/>
+      <c r="E8" s="40"/>
+      <c r="F8" s="41"/>
+      <c r="G8" s="42"/>
+      <c r="H8" s="43" t="s">
         <v>4</v>
       </c>
-      <c r="I8" s="15"/>
-      <c r="J8" s="16"/>
-      <c r="K8" s="17"/>
-      <c r="L8" s="18"/>
-      <c r="M8" s="19" t="s">
+      <c r="I8" s="44"/>
+      <c r="J8" s="45"/>
+      <c r="K8" s="46"/>
+      <c r="L8" s="47"/>
+      <c r="M8" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="N8" s="20"/>
-      <c r="O8" s="21"/>
-      <c r="P8" s="22"/>
-      <c r="Q8" s="22"/>
-      <c r="R8" s="23"/>
+      <c r="N8" s="39"/>
+      <c r="O8" s="40"/>
+      <c r="P8" s="41"/>
+      <c r="Q8" s="41"/>
+      <c r="R8" s="42"/>
     </row>
     <row r="9" spans="1:18" ht="22.8" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="46"/>
-      <c r="B9" s="47"/>
-      <c r="C9" s="42" t="s">
+      <c r="A9" s="36"/>
+      <c r="B9" s="37"/>
+      <c r="C9" s="32" t="s">
         <v>25</v>
       </c>
-      <c r="D9" s="43"/>
-      <c r="E9" s="39"/>
-      <c r="F9" s="40"/>
-      <c r="G9" s="41"/>
-      <c r="H9" s="42" t="s">
+      <c r="D9" s="33"/>
+      <c r="E9" s="29"/>
+      <c r="F9" s="30"/>
+      <c r="G9" s="31"/>
+      <c r="H9" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="I9" s="43"/>
-      <c r="J9" s="39"/>
-      <c r="K9" s="40"/>
-      <c r="L9" s="41"/>
-      <c r="M9" s="42" t="s">
+      <c r="I9" s="33"/>
+      <c r="J9" s="29"/>
+      <c r="K9" s="30"/>
+      <c r="L9" s="31"/>
+      <c r="M9" s="32" t="s">
         <v>26</v>
       </c>
-      <c r="N9" s="43"/>
-      <c r="O9" s="39"/>
-      <c r="P9" s="40"/>
-      <c r="Q9" s="40"/>
-      <c r="R9" s="41"/>
+      <c r="N9" s="33"/>
+      <c r="O9" s="29"/>
+      <c r="P9" s="30"/>
+      <c r="Q9" s="30"/>
+      <c r="R9" s="31"/>
     </row>
     <row r="10" spans="1:18" ht="22.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="46"/>
-      <c r="B10" s="47"/>
-      <c r="C10" s="35" t="s">
+      <c r="A10" s="36"/>
+      <c r="B10" s="37"/>
+      <c r="C10" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="36"/>
+      <c r="D10" s="26"/>
       <c r="E10" s="50"/>
       <c r="F10" s="51"/>
       <c r="G10" s="52"/>
-      <c r="H10" s="37" t="s">
+      <c r="H10" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="I10" s="38"/>
-      <c r="J10" s="39"/>
-      <c r="K10" s="40"/>
-      <c r="L10" s="41"/>
-      <c r="M10" s="42" t="s">
+      <c r="I10" s="28"/>
+      <c r="J10" s="29"/>
+      <c r="K10" s="30"/>
+      <c r="L10" s="31"/>
+      <c r="M10" s="32" t="s">
         <v>27</v>
       </c>
-      <c r="N10" s="43"/>
+      <c r="N10" s="33"/>
       <c r="O10" s="50"/>
       <c r="P10" s="51"/>
       <c r="Q10" s="51"/>
       <c r="R10" s="52"/>
     </row>
     <row r="11" spans="1:18" ht="71.400000000000006" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="27" t="s">
+      <c r="A11" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="B11" s="28"/>
-      <c r="C11" s="29"/>
-      <c r="D11" s="30"/>
-      <c r="E11" s="30"/>
-      <c r="F11" s="30"/>
-      <c r="G11" s="30"/>
-      <c r="H11" s="30"/>
-      <c r="I11" s="30"/>
-      <c r="J11" s="30"/>
-      <c r="K11" s="30"/>
-      <c r="L11" s="30"/>
-      <c r="M11" s="30"/>
-      <c r="N11" s="30"/>
-      <c r="O11" s="30"/>
-      <c r="P11" s="30"/>
-      <c r="Q11" s="30"/>
-      <c r="R11" s="31"/>
+      <c r="B11" s="18"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="20"/>
+      <c r="E11" s="20"/>
+      <c r="F11" s="20"/>
+      <c r="G11" s="20"/>
+      <c r="H11" s="20"/>
+      <c r="I11" s="20"/>
+      <c r="J11" s="20"/>
+      <c r="K11" s="20"/>
+      <c r="L11" s="20"/>
+      <c r="M11" s="20"/>
+      <c r="N11" s="20"/>
+      <c r="O11" s="20"/>
+      <c r="P11" s="20"/>
+      <c r="Q11" s="20"/>
+      <c r="R11" s="21"/>
     </row>
     <row r="12" spans="1:18" ht="71.400000000000006" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="27" t="s">
+      <c r="A12" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="B12" s="28"/>
-      <c r="C12" s="29"/>
-      <c r="D12" s="30"/>
-      <c r="E12" s="30"/>
-      <c r="F12" s="30"/>
-      <c r="G12" s="30"/>
-      <c r="H12" s="30"/>
-      <c r="I12" s="30"/>
-      <c r="J12" s="30"/>
-      <c r="K12" s="30"/>
-      <c r="L12" s="30"/>
-      <c r="M12" s="30"/>
-      <c r="N12" s="30"/>
-      <c r="O12" s="30"/>
-      <c r="P12" s="30"/>
-      <c r="Q12" s="30"/>
-      <c r="R12" s="31"/>
+      <c r="B12" s="18"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="20"/>
+      <c r="E12" s="20"/>
+      <c r="F12" s="20"/>
+      <c r="G12" s="20"/>
+      <c r="H12" s="20"/>
+      <c r="I12" s="20"/>
+      <c r="J12" s="20"/>
+      <c r="K12" s="20"/>
+      <c r="L12" s="20"/>
+      <c r="M12" s="20"/>
+      <c r="N12" s="20"/>
+      <c r="O12" s="20"/>
+      <c r="P12" s="20"/>
+      <c r="Q12" s="20"/>
+      <c r="R12" s="21"/>
     </row>
     <row r="13" spans="1:18" ht="71.400000000000006" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="27" t="s">
+      <c r="A13" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="B13" s="28"/>
-      <c r="C13" s="29"/>
-      <c r="D13" s="30"/>
-      <c r="E13" s="30"/>
-      <c r="F13" s="30"/>
-      <c r="G13" s="30"/>
-      <c r="H13" s="30"/>
-      <c r="I13" s="30"/>
-      <c r="J13" s="30"/>
-      <c r="K13" s="30"/>
-      <c r="L13" s="30"/>
-      <c r="M13" s="30"/>
-      <c r="N13" s="30"/>
-      <c r="O13" s="30"/>
-      <c r="P13" s="30"/>
-      <c r="Q13" s="30"/>
-      <c r="R13" s="31"/>
+      <c r="B13" s="18"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="20"/>
+      <c r="F13" s="20"/>
+      <c r="G13" s="20"/>
+      <c r="H13" s="20"/>
+      <c r="I13" s="20"/>
+      <c r="J13" s="20"/>
+      <c r="K13" s="20"/>
+      <c r="L13" s="20"/>
+      <c r="M13" s="20"/>
+      <c r="N13" s="20"/>
+      <c r="O13" s="20"/>
+      <c r="P13" s="20"/>
+      <c r="Q13" s="20"/>
+      <c r="R13" s="21"/>
     </row>
     <row r="14" spans="1:18" ht="71.400000000000006" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="27" t="s">
+      <c r="A14" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B14" s="28"/>
-      <c r="C14" s="32"/>
-      <c r="D14" s="33"/>
-      <c r="E14" s="33"/>
-      <c r="F14" s="33"/>
-      <c r="G14" s="33"/>
-      <c r="H14" s="33"/>
-      <c r="I14" s="33"/>
-      <c r="J14" s="33"/>
-      <c r="K14" s="33"/>
-      <c r="L14" s="33"/>
-      <c r="M14" s="33"/>
-      <c r="N14" s="33"/>
-      <c r="O14" s="33"/>
-      <c r="P14" s="33"/>
-      <c r="Q14" s="33"/>
-      <c r="R14" s="34"/>
+      <c r="B14" s="18"/>
+      <c r="C14" s="22"/>
+      <c r="D14" s="23"/>
+      <c r="E14" s="23"/>
+      <c r="F14" s="23"/>
+      <c r="G14" s="23"/>
+      <c r="H14" s="23"/>
+      <c r="I14" s="23"/>
+      <c r="J14" s="23"/>
+      <c r="K14" s="23"/>
+      <c r="L14" s="23"/>
+      <c r="M14" s="23"/>
+      <c r="N14" s="23"/>
+      <c r="O14" s="23"/>
+      <c r="P14" s="23"/>
+      <c r="Q14" s="23"/>
+      <c r="R14" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="41">
@@ -1543,6 +1543,12 @@
     <mergeCell ref="A7:B10"/>
     <mergeCell ref="C9:D9"/>
     <mergeCell ref="C8:D8"/>
+    <mergeCell ref="M8:N8"/>
+    <mergeCell ref="M7:N7"/>
+    <mergeCell ref="E8:G8"/>
+    <mergeCell ref="E7:G7"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="J8:L8"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="A12:B12"/>
@@ -1551,10 +1557,6 @@
     <mergeCell ref="C12:R12"/>
     <mergeCell ref="C13:R13"/>
     <mergeCell ref="C14:R14"/>
-    <mergeCell ref="M8:N8"/>
-    <mergeCell ref="M7:N7"/>
-    <mergeCell ref="E8:G8"/>
-    <mergeCell ref="E7:G7"/>
     <mergeCell ref="J3:L3"/>
     <mergeCell ref="J5:L5"/>
     <mergeCell ref="M5:R5"/>
@@ -1562,8 +1564,6 @@
     <mergeCell ref="C7:D7"/>
     <mergeCell ref="H7:I7"/>
     <mergeCell ref="J7:L7"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="J8:L8"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
